--- a/artfynd/A 68096-2021 artfynd.xlsx
+++ b/artfynd/A 68096-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68096-2021 artfynd.xlsx
+++ b/artfynd/A 68096-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98371340</v>
+        <v>98371211</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544857.6249320203</v>
+        <v>544859</v>
       </c>
       <c r="R2" t="n">
-        <v>6347946.351600104</v>
+        <v>6347925</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,24 +745,14 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ett 20-tal</t>
+          <t>Ett 100-tal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98371211</v>
+        <v>98371282</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544859.4921386163</v>
+        <v>544861</v>
       </c>
       <c r="R3" t="n">
-        <v>6347924.203414281</v>
+        <v>6347950</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,24 +849,14 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett 100-tal</t>
+          <t>Ett 15-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98372860</v>
+        <v>98371340</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,11 +911,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -959,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544874.7542299231</v>
+        <v>544858</v>
       </c>
       <c r="R4" t="n">
-        <v>6347915.718963633</v>
+        <v>6347946</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,19 +953,14 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,12 +990,7 @@
         <v>98371547</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544859.0567342577</v>
+        <v>544859</v>
       </c>
       <c r="R5" t="n">
-        <v>6347914.46607302</v>
+        <v>6347914</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,19 +1057,9 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-01-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98371282</v>
+        <v>98371671</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1119,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544860.2920746324</v>
+        <v>544817</v>
       </c>
       <c r="R6" t="n">
-        <v>6347950.165600883</v>
+        <v>6347914</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,24 +1165,9 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-01-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett 15-tal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,15 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98371671</v>
+        <v>98371697</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,11 +1222,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544816.8041045557</v>
+        <v>544804</v>
       </c>
       <c r="R7" t="n">
-        <v>6347914.00477222</v>
+        <v>6347921</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1348,19 +1264,14 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett 10-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,15 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98371697</v>
+        <v>98372860</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1326,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1429,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544803.7207230096</v>
+        <v>544875</v>
       </c>
       <c r="R8" t="n">
-        <v>6347921.431809202</v>
+        <v>6347915</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,24 +1372,9 @@
           <t>2022-01-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-01-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett 10-tal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,6 +1398,110 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>98373002</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>544917</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6347912</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tveta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-01-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-01-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ett 10-tal</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68096-2021 artfynd.xlsx
+++ b/artfynd/A 68096-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98371211</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98371282</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98371340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98371547</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98371671</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98371697</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98372860</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,8 +1542,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98373002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>